--- a/Daily Activity Tracker/Daily_Activity_Tracker_October.xlsx
+++ b/Daily Activity Tracker/Daily_Activity_Tracker_October.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chandrakanb\chandrakanb\Daily Activity Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6FB8EE-7723-4A3B-BF9B-2E45B9E0E144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9697C7-4A57-41CD-B31E-9AB87BD4FC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="day_month" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,19 @@
     <sheet name="4th_October" sheetId="4" r:id="rId4"/>
     <sheet name="14th_October" sheetId="5" r:id="rId5"/>
     <sheet name="15th_October" sheetId="6" r:id="rId6"/>
-    <sheet name="16th_October" sheetId="8" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId8"/>
+    <sheet name="16th_October" sheetId="7" r:id="rId7"/>
+    <sheet name="17th_October" sheetId="8" r:id="rId8"/>
+    <sheet name="18th_October" sheetId="9" r:id="rId9"/>
+    <sheet name="19th_October" sheetId="10" r:id="rId10"/>
+    <sheet name="21st_October" sheetId="11" r:id="rId11"/>
+    <sheet name="22nd_October" sheetId="12" r:id="rId12"/>
+    <sheet name="23rd_October" sheetId="13" r:id="rId13"/>
+    <sheet name="28th_October" sheetId="14" r:id="rId14"/>
+    <sheet name="24th_October" sheetId="15" r:id="rId15"/>
+    <sheet name="25th_October" sheetId="16" r:id="rId16"/>
+    <sheet name="29th_October" sheetId="17" r:id="rId17"/>
+    <sheet name="30th_October" sheetId="19" r:id="rId18"/>
+    <sheet name="Trash" sheetId="18" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="164">
   <si>
     <t xml:space="preserve">Sr.No. </t>
   </si>
@@ -222,27 +233,6 @@
     <t>Share logs for USB Disconnection after ACC Cycle</t>
   </si>
   <si>
-    <t>No. of Skeleton Created</t>
-  </si>
-  <si>
-    <t>No. Of TC Executed</t>
-  </si>
-  <si>
-    <t>No. of TCs Sent for review</t>
-  </si>
-  <si>
-    <t>Executed on which Bench</t>
-  </si>
-  <si>
-    <t>Added in Pack or not</t>
-  </si>
-  <si>
-    <t>No. of TCs for Rework</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Executed the failed Overnight Failed Test Script:
 "KPIT_TC_DRT_CAT_005": Re-executed the Test Script in daytime</t>
   </si>
@@ -262,6 +252,9 @@
     <t>Installed Kite build 200.16 on Bench 11.</t>
   </si>
   <si>
+    <t>Performed Basic Sanity on Bench 11.</t>
+  </si>
+  <si>
     <t>Given KT on Bench Hardwares(Connected peripherals) to new team members.</t>
   </si>
   <si>
@@ -283,7 +276,315 @@
     <t>Taken git pull/push and checked missing resource popup on Bench 09.</t>
   </si>
   <si>
-    <t>Performed Basic Sanity on Bench 11.</t>
+    <t>Feasibility of new test script development "KPIT_TC_DRT_BTA_032"</t>
+  </si>
+  <si>
+    <t>Given KT on ADB overview(ADB commands used) to new team members.</t>
+  </si>
+  <si>
+    <t>Done feasibility of test scripts for the test script movement activity.</t>
+  </si>
+  <si>
+    <t>Flashed 30AA Variant on the Bench05 and Bench08.</t>
+  </si>
+  <si>
+    <t>Taken git pull/push on Bench 09.</t>
+  </si>
+  <si>
+    <t>Replaced Config files for the "DDev_705_Repo" on Bench09.</t>
+  </si>
+  <si>
+    <t>Checked missing resource popup on Bench 09.</t>
+  </si>
+  <si>
+    <t>Flashed Base Build on manual T Variant Bench.</t>
+  </si>
+  <si>
+    <t>Flashed Last build on manual T Variant Bench.</t>
+  </si>
+  <si>
+    <t>T90X Variant Flashing on Bench 01 and Bench 03.</t>
+  </si>
+  <si>
+    <t>Flashed Base Build on Bench 09.</t>
+  </si>
+  <si>
+    <t>Flashed Last build on Bench 09.</t>
+  </si>
+  <si>
+    <t>PW-241</t>
+  </si>
+  <si>
+    <t>Published the Overnight Execution Reports of Bench 06.</t>
+  </si>
+  <si>
+    <t>Auto-Flashing Analysis on Bench 06.</t>
+  </si>
+  <si>
+    <t>PW-235</t>
+  </si>
+  <si>
+    <t>Overnight Execution Analysis of Bench 06.</t>
+  </si>
+  <si>
+    <t>Attended the DSR 2nd Meeting.</t>
+  </si>
+  <si>
+    <t>Flashed Base Build on Bench 06</t>
+  </si>
+  <si>
+    <t>Flashed Last build on Bench 06</t>
+  </si>
+  <si>
+    <t>Taken git pull/push on Bench 06.</t>
+  </si>
+  <si>
+    <t>Taken git pull/push on Bench 07.</t>
+  </si>
+  <si>
+    <t>Bench 06 failure fixation.</t>
+  </si>
+  <si>
+    <t>Bench 07 failure fixation.</t>
+  </si>
+  <si>
+    <t>Bench 09 failure fixation.
+- TS Movement</t>
+  </si>
+  <si>
+    <t>Updated the Test Script Movement Sheet</t>
+  </si>
+  <si>
+    <t>Updated WiFi Issues DRT Automation Sheet</t>
+  </si>
+  <si>
+    <t>Performed Calibration Activity on Bench 09.</t>
+  </si>
+  <si>
+    <t>Checked the below scripts using CAN Tool A1 on Bench 09.
+- "KPIT_TC_DRT_IDS_002"
+- "KPIT_TC_DRT_IDS_011"</t>
+  </si>
+  <si>
+    <t>Connected Sound Blaster and Impedance Convertor to Bench 07.</t>
+  </si>
+  <si>
+    <t>Flashed T90X Variant on the Bench01 and Bench03.</t>
+  </si>
+  <si>
+    <t>Manual Bench</t>
+  </si>
+  <si>
+    <t>Automation Bench</t>
+  </si>
+  <si>
+    <t>CAN Tool A1</t>
+  </si>
+  <si>
+    <t>Vector</t>
+  </si>
+  <si>
+    <t>Vehicle Simulator</t>
+  </si>
+  <si>
+    <t>Meter Simulator</t>
+  </si>
+  <si>
+    <t>Given KT to new team members on Function Block Creation and Resourecs</t>
+  </si>
+  <si>
+    <t>Checked the CAN frames CAN Tool A1 on Manual Bench for follwowing scripts
+- KPIT_TC_DRT_002
+- KPIT_TC_DRT_011</t>
+  </si>
+  <si>
+    <t>Flashed 30AA Variant on the Bench01 and Bench03.</t>
+  </si>
+  <si>
+    <t>Supported in creating config files for Bench 01 and Bench 03</t>
+  </si>
+  <si>
+    <t>Shared the python file to eject usb drive.</t>
+  </si>
+  <si>
+    <t>Checked and resolved  the appium issue on phone for Bench 11.</t>
+  </si>
+  <si>
+    <t>Created Skelaton for new test script
+- KPIT_TC_DRT_BTA_032</t>
+  </si>
+  <si>
+    <t>Flashed yesterday's build on bench 03</t>
+  </si>
+  <si>
+    <t>Executed the failed Testscripts in daytime 
+- KPIT_TC_DRT_KEY_013</t>
+  </si>
+  <si>
+    <t>Created and executed new test script
+- KPIT_TC_DRT_BTA_032</t>
+  </si>
+  <si>
+    <t>Attached reports on KAP
+- KPIT_TC_DRT_BTA_032</t>
+  </si>
+  <si>
+    <t>Performed calibration activity of Bench 09.</t>
+  </si>
+  <si>
+    <t>Feasibility of Test Scripts related to Meter and Vehicle Simulator through Vector CAN.</t>
+  </si>
+  <si>
+    <t>Fixed Audio setup on Bench 07.</t>
+  </si>
+  <si>
+    <t>Breakfast</t>
+  </si>
+  <si>
+    <t>Given data to Sahil for IP Reservation of Bench 09.</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>IP Reservation on Bench 09.</t>
+  </si>
+  <si>
+    <t>Updated Wait upto "500" in "Go to Homescreen" FB</t>
+  </si>
+  <si>
+    <t>Executed the Failed Pre/Post-Condition for Daytime execution</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>Feasibility of the Vehicle simulator related testscript through vector.</t>
+  </si>
+  <si>
+    <t>No. of Skeleton Created</t>
+  </si>
+  <si>
+    <t>No. Of TC Executed</t>
+  </si>
+  <si>
+    <t>No. of TCs Sent for review</t>
+  </si>
+  <si>
+    <t>Executed on which Bench</t>
+  </si>
+  <si>
+    <t>Added in Pack or not</t>
+  </si>
+  <si>
+    <t>No. of TCs for Rework</t>
+  </si>
+  <si>
+    <t>49_Bench01_30AA_T90X_KA_USB_Audio_A13_2_2</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>08_Bench01_30AA_T90X_KA_WLC_A13_2_2</t>
+  </si>
+  <si>
+    <t>44_Bench01_30AA_T90X_KA_SSR_DryRun2.3</t>
+  </si>
+  <si>
+    <t>25_Bench01_30AA_T90X_KA_DAB_DryRun2.4</t>
+  </si>
+  <si>
+    <t>56_Bench01_30AA_T90X_KA_AMFM_2.4Dry_Run</t>
+  </si>
+  <si>
+    <t>61_Bench01_T90X_KA_AVC_DryRun2.4</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>1_Bench01_30AA_T90X_KA_Compass_A13_DryRun_2_1</t>
+  </si>
+  <si>
+    <t>Working(3:34:07 hrs)[without AF]</t>
+  </si>
+  <si>
+    <t>22_Bench01_30AA_T90X_KA_AMFM_A13_DryRun_2_1</t>
+  </si>
+  <si>
+    <t>10 00 00 03 00 00 00 00</t>
+  </si>
+  <si>
+    <t>TYAW</t>
+  </si>
+  <si>
+    <t>24_Bench01_30AA_T90X_KA_WLC_A13_DryRun_2_1</t>
+  </si>
+  <si>
+    <t>F0 00 00 03 00 00 00 00</t>
+  </si>
+  <si>
+    <t>KITE Version : 200.11
+Total: 27
+Pass: 25
+Fail: 02
+Stabilized TS: 25</t>
+  </si>
+  <si>
+    <t>25_Bench01_30AA_T90X_KA_Vehicle_Setting_A13 _DryRun_2_1</t>
+  </si>
+  <si>
+    <t>27_Bench01_30AA_T90X_KA_Meter_A13_DryRun_2_1</t>
+  </si>
+  <si>
+    <t>ICB Issue(1 TS):
+	1. CAN signal not reflected(1)</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Test script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failure reason </t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>KPIT_TC_DRT_KEY_013</t>
+  </si>
+  <si>
+    <t>USB Device Disconnected after ACC cycle</t>
+  </si>
+  <si>
+    <t>Executed in daytime, Passed.</t>
+  </si>
+  <si>
+    <t>Connected Bench 09 to PMT Jenkins Pipeline.</t>
+  </si>
+  <si>
+    <t>Re-executed the failed testdcript in daytime.</t>
+  </si>
+  <si>
+    <t>Prepared the sheet format for the vehicle simulator related can signals analysis.</t>
   </si>
 </sst>
 </file>
@@ -293,7 +594,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +625,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Work Sans"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -345,7 +670,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -647,11 +972,114 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -736,11 +1164,310 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1541,13 +2268,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="52" priority="1">
       <formula>SEARCH("In-Progress", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="51" priority="2">
       <formula>SEARCH("Incomplete", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="3">
+    <cfRule type="expression" dxfId="50" priority="3">
       <formula>SEARCH("Completed", F2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1556,6 +2283,4048 @@
       <formula1>"Completed, Incomplete, In-Progress"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="45">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.4375</v>
+      </c>
+      <c r="D2" s="46">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="E2" s="46">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>1.0416666666666685E-2</v>
+      </c>
+      <c r="F2" s="47"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="48">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="E4" s="14">
+        <f t="shared" si="1"/>
+        <v>2.4305555555555525E-2</v>
+      </c>
+      <c r="F4" s="49"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="41">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="55">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D5" s="50">
+        <v>0.4375</v>
+      </c>
+      <c r="E5" s="50">
+        <f t="shared" si="1"/>
+        <v>1.0416666666666685E-2</v>
+      </c>
+      <c r="F5" s="42"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="45">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46">
+        <f t="shared" si="1"/>
+        <v>-0.47569444444444442</v>
+      </c>
+      <c r="F6" s="47"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="48">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="E8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="F8" s="49"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="45">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46">
+        <f t="shared" si="1"/>
+        <v>-0.54166666666666663</v>
+      </c>
+      <c r="F9" s="47"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>-0.40069444444444441</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="38"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D30" s="38"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D31" s="38"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.40347222222222218</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>4.8611111111111494E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>1.388888888888884E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444753E-3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.49166666666666659</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>5.5555555555554803E-3</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.49166666666666659</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>1.388888888888995E-3</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="D21" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444445308E-3</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>0.13472222222222235</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="25" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>1.388888888888884E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222654E-3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.44513888888888892</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>2.8472222222222232E-2</v>
+      </c>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>3.6805555555555591E-2</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="22" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>4.1666666666667074E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444198E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.4375</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444198E-3</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>6.2500000000000056E-2</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>0.9111111111111112</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="58"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D28" s="57"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="25"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D30" s="25"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="19" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0C00-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.40625</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>1.0416666666666685E-2</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.40625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444198E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222654E-3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>1.041666666666663E-2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444753E-3</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>-0.58888888888888891</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>-0.55069444444444438</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="16" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0D00-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.43333333333333329</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>6.2499999999999778E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.43333333333333329</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.43958333333333333</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>6.2500000000000333E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.43958333333333333</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.44027777777777782</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444449749E-4</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>-0.46527777777777779</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>2.777777777777779E-2</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>2.777777777777779E-2</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>-0.32361111111111107</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D28" s="57"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="25"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D30" s="25"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="13" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0E00-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51736111111111116</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>1.0416666666666741E-2</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.51736111111111116</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>6.2499999999999778E-3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.53125</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>1.041666666666663E-2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>1.0416666666666741E-2</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>4.0972222222222299E-2</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="10" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0F00-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>9.0277777777777457E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>6.9444444444444753E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>6.597222222222221E-2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>8.5416666666666641E-2</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-1000-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{6B60F373-641C-4930-AA94-171B2B8C32A6}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:W25"/>
+  <sheetFormatPr defaultColWidth="12.21875" defaultRowHeight="19.8" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="19" width="3.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32">
+        <v>0</v>
+      </c>
+      <c r="B2" s="33">
+        <v>0</v>
+      </c>
+      <c r="C2" s="33">
+        <v>0</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="34">
+        <v>0</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>8</v>
+      </c>
+      <c r="Q2">
+        <v>4</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>6</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H4" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="L5" s="73">
+        <v>2</v>
+      </c>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="73">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H6" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" t="s">
+        <v>141</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" t="s">
+        <v>144</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
+      <c r="W10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="V11">
+        <v>7</v>
+      </c>
+      <c r="W11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="V12">
+        <v>8</v>
+      </c>
+      <c r="W12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V13">
+        <v>9</v>
+      </c>
+      <c r="W13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V14" t="s">
+        <v>149</v>
+      </c>
+      <c r="W14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V15" t="s">
+        <v>150</v>
+      </c>
+      <c r="W15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V16" t="s">
+        <v>151</v>
+      </c>
+      <c r="W16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>152</v>
+      </c>
+      <c r="W17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V18" t="s">
+        <v>153</v>
+      </c>
+      <c r="W18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V19" t="s">
+        <v>154</v>
+      </c>
+      <c r="W19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="69" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="70" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="65"/>
+    </row>
+    <row r="25" spans="1:23" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="P5:S5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1995,13 +6764,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>SEARCH("In-Progress", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="48" priority="2">
       <formula>SEARCH("Incomplete", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="47" priority="3">
       <formula>SEARCH("Completed", F2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2478,24 +7247,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="46" priority="4">
       <formula>SEARCH("In-Progress", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="5">
+    <cfRule type="expression" dxfId="45" priority="5">
       <formula>SEARCH("Incomplete", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="44" priority="6">
       <formula>SEARCH("Completed", F2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>SEARCH("In-Progress", F24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="42" priority="2">
       <formula>SEARCH("Incomplete", F24)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="41" priority="3">
       <formula>SEARCH("Completed", F24)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3279,13 +8048,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>SEARCH("In-Progress", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>SEARCH("Incomplete", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>SEARCH("Completed", F2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3694,13 +8463,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>SEARCH("In-Progress", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="36" priority="2">
       <formula>SEARCH("Incomplete", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="35" priority="3">
       <formula>SEARCH("Completed", F2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3714,7 +8483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3758,7 +8527,7 @@
         <v>0.40625</v>
       </c>
       <c r="E2" s="8">
-        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <f>D2-C2</f>
         <v>1.0416666666666685E-2</v>
       </c>
       <c r="F2" s="9" t="s">
@@ -3780,7 +8549,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" si="1"/>
+        <f>D3-C3</f>
         <v>6.9444444444444198E-3</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -3802,7 +8571,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E4" s="8">
-        <f t="shared" si="1"/>
+        <f>D4-C4</f>
         <v>1.0416666666666685E-2</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -3824,20 +8593,20 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="1"/>
+        <f>D5-C5</f>
         <v>2.430555555555558E-2</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C6" s="11">
         <v>0.44791666666666669</v>
@@ -3859,7 +8628,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C7" s="11">
         <v>0.47916666666666669</v>
@@ -3868,20 +8637,20 @@
         <v>0.5</v>
       </c>
       <c r="E7" s="8">
-        <f>D6-C6</f>
+        <f t="shared" ref="E7:E21" si="1">D6-C6</f>
         <v>3.125E-2</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C8" s="11">
         <v>0.52083333333333337</v>
@@ -3890,7 +8659,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" ref="E8:E21" si="2">D7-C7</f>
+        <f t="shared" si="1"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -3903,7 +8672,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C9" s="11">
         <v>0.61527777777777781</v>
@@ -3912,7 +8681,7 @@
         <v>0.62152777777777779</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -3925,7 +8694,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C10" s="11">
         <v>0.62152777777777779</v>
@@ -3934,7 +8703,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6.2499999999999778E-3</v>
       </c>
       <c r="F10" s="9" t="s">
@@ -3947,7 +8716,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C11" s="11">
         <v>0.63541666666666663</v>
@@ -3956,7 +8725,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.388888888888884E-2</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -3969,7 +8738,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C12" s="11">
         <v>0.64583333333333337</v>
@@ -3978,25 +8747,25 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.0416666666666741E-2</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.0833333333333259E-2</v>
       </c>
       <c r="F13" s="9" t="s">
@@ -4009,66 +8778,66 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F17" s="9" t="s">
@@ -4081,30 +8850,30 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F19" s="9" t="s">
@@ -4122,7 +8891,7 @@
       <c r="C20" s="11"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F20" s="9" t="s">
@@ -4140,7 +8909,7 @@
       <c r="C21" s="11"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F21" s="9" t="s">
@@ -4162,18 +8931,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>SEARCH("In-Progress", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="33" priority="2">
       <formula>SEARCH("Incomplete", F2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="32" priority="3">
       <formula>SEARCH("Completed", F2)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{6DA33634-793B-442C-8951-232DEECC670D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Completed, Incomplete, In-Progress"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4182,59 +8951,810 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="12.21875" defaultRowHeight="19.8" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32">
-        <v>0</v>
-      </c>
-      <c r="B2" s="33">
-        <v>0</v>
-      </c>
-      <c r="C2" s="33">
-        <v>0</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="34">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.39374999999999999</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>5.5555555555555913E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>8.5416666666666696E-2</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="38"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="39"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="39"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="31" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0700-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
+    <col min="3" max="5" width="10.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A21" si="0">ROW() - ROW($A$1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="E2" s="8">
+        <f t="shared" ref="E2:E21" si="1">D2-C2</f>
+        <v>6.9444444444444753E-3</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.40625</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4722222222222099E-3</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.40625</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="1"/>
+        <v>1.0416666666666685E-2</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18">
+        <f>SUM(E2:E21)</f>
+        <v>2.083333333333337E-2</v>
+      </c>
+      <c r="F22" s="19"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="28" priority="1">
+      <formula>SEARCH("In-Progress", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="2">
+      <formula>SEARCH("Incomplete", F2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="3">
+      <formula>SEARCH("Completed", F2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0800-000000000000}">
+      <formula1>"Completed, Incomplete, In-Progress"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>